--- a/sql-audit/assets/应用代码扫描结果模板.xlsx
+++ b/sql-audit/assets/应用代码扫描结果模板.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\All\xinju\AI-9\sql-audit\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8686C61E-CC95-4FDD-AF07-BFA23FD092E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96FAFD47-7F1D-459B-B30D-E19A5FF3BA67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="70" yWindow="1140" windowWidth="25530" windowHeight="13550" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="审核结果" sheetId="1" r:id="rId1"/>
+    <sheet name="汇总信息" sheetId="2" r:id="rId2"/>
+    <sheet name="规则列表" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="103">
   <si>
     <t>人工复核结果</t>
   </si>
@@ -76,13 +78,275 @@
   </si>
   <si>
     <t>1. 使用绑定变量替代业务常量。</t>
+  </si>
+  <si>
+    <t>代码审核规则</t>
+  </si>
+  <si>
+    <t>更新日期: 2026-08-18 | 共13条规则 | 仅包含当前应用代码 SQL 审核规则</t>
+  </si>
+  <si>
+    <t>规则编号</t>
+  </si>
+  <si>
+    <t>规则级别</t>
+  </si>
+  <si>
+    <t>适用范围</t>
+  </si>
+  <si>
+    <t>适用数据库</t>
+  </si>
+  <si>
+    <t>规则内容</t>
+  </si>
+  <si>
+    <t>审核方式</t>
+  </si>
+  <si>
+    <t>BUS-001</t>
+  </si>
+  <si>
+    <t>硬性</t>
+  </si>
+  <si>
+    <t>业务SQL内容审核</t>
+  </si>
+  <si>
+    <t>通用</t>
+  </si>
+  <si>
+    <t>严禁包含DDL操作（TRUNCATE/CREATE/ALTER/DROP等结构变更），适用于业务SQL及存储过程内部SQL</t>
+  </si>
+  <si>
+    <t>检查SQL是否包含DDL关键字</t>
+  </si>
+  <si>
+    <t>业务SQL包含禁止的DDL操作：检测到结构变更语句。</t>
+  </si>
+  <si>
+    <t>将结构变更移出业务SQL，按DDL流程单独提交。</t>
+  </si>
+  <si>
+    <t>BUS-002</t>
+  </si>
+  <si>
+    <t>DELETE/UPDATE必须有有效WHERE（WHERE 1=1 AND id=?含限制条件不算违规）</t>
+  </si>
+  <si>
+    <t>检查DELETE/UPDATE是否包含有效WHERE</t>
+  </si>
+  <si>
+    <t>无条件全表更新/删除：语句缺少有效WHERE条件；位置：业务SQL。</t>
+  </si>
+  <si>
+    <t>增加能够限定本次业务数据范围的有效条件。</t>
+  </si>
+  <si>
+    <t>BUS-003</t>
+  </si>
+  <si>
+    <t>禁止SELECT *和alias.*</t>
+  </si>
+  <si>
+    <t>检查SELECT列表是否使用*</t>
+  </si>
+  <si>
+    <t>使用SELECT *：未明确列出所需字段。</t>
+  </si>
+  <si>
+    <t>只列出业务实际需要的字段。</t>
+  </si>
+  <si>
+    <t>BUS-004</t>
+  </si>
+  <si>
+    <t>必须使用绑定变量占位（?/:name/$1等），禁止硬编码常量。示例值由MAT-011检查</t>
+  </si>
+  <si>
+    <t>检查SQL是否使用绑定占位</t>
+  </si>
+  <si>
+    <t>绑定变量使用不符合要求：业务参数未使用占位。</t>
+  </si>
+  <si>
+    <t>使用绑定变量替代业务常量。</t>
+  </si>
+  <si>
+    <t>BUS-005</t>
+  </si>
+  <si>
+    <t>NULL判断必须使用IS NULL/IS NOT NULL，禁止= NULL/!= NULL</t>
+  </si>
+  <si>
+    <t>检查NULL判断语法</t>
+  </si>
+  <si>
+    <t>NULL判断错误：使用了与NULL的等值或不等值比较。</t>
+  </si>
+  <si>
+    <t>改用IS NULL或IS NOT NULL。</t>
+  </si>
+  <si>
+    <t>BUS-006</t>
+  </si>
+  <si>
+    <t>建议</t>
+  </si>
+  <si>
+    <t>尽量避免NOT/!=/&lt;&gt;/NOT EXISTS/NOT IN等负向查询</t>
+  </si>
+  <si>
+    <t>检查负向查询条件，有则提示风险</t>
+  </si>
+  <si>
+    <t>负向查询风险：使用了&lt;operator&gt;，可能导致索引利用不足；位置：WHERE条件。</t>
+  </si>
+  <si>
+    <t>优先改写为正向条件；无法改写时补充执行计划、数据量和业务必要性供二次确认。</t>
+  </si>
+  <si>
+    <t>BUS-007</t>
+  </si>
+  <si>
+    <t>同一字段多等值OR必须改写为IN()（不同字段间OR不适用）</t>
+  </si>
+  <si>
+    <t>检查同字段是否使用多个OR连接</t>
+  </si>
+  <si>
+    <t>同字段重复OR：同一字段的多个等值条件未使用IN。</t>
+  </si>
+  <si>
+    <t>将同字段等值OR改写为IN(...)。</t>
+  </si>
+  <si>
+    <t>BUS-008</t>
+  </si>
+  <si>
+    <t>禁止前导通配查询（LIKE %xx和LIKE %xx%）</t>
+  </si>
+  <si>
+    <t>检查LIKE模式是否以%开头</t>
+  </si>
+  <si>
+    <t>前导通配查询：LIKE参数以'%'开始，可能无法使用普通索引。</t>
+  </si>
+  <si>
+    <t>改为精确或前缀匹配；业务必须包含匹配时提交必要性和影响说明供二次确认。</t>
+  </si>
+  <si>
+    <t>BUS-009</t>
+  </si>
+  <si>
+    <t>JOIN不得超过3张表（同表不同别名按实际计数）</t>
+  </si>
+  <si>
+    <t>统计JOIN的表数量</t>
+  </si>
+  <si>
+    <t>多表关联超过上限：业务SQL JOIN超过3张表。</t>
+  </si>
+  <si>
+    <t>改为分步查询、应用层组装或字段冗余方案。</t>
+  </si>
+  <si>
+    <t>BUS-010</t>
+  </si>
+  <si>
+    <t>必须使用ANSI JOIN语法（INNER JOIN/LEFT JOIN），禁止逗号分隔隐式连接</t>
+  </si>
+  <si>
+    <t>检查JOIN语法是否为标准ANSI写法</t>
+  </si>
+  <si>
+    <t>使用逗号隐式连接：未采用ANSI JOIN语法。</t>
+  </si>
+  <si>
+    <t>改用INNER JOIN、LEFT JOIN等明确连接方式和ON条件。</t>
+  </si>
+  <si>
+    <t>BUS-011</t>
+  </si>
+  <si>
+    <t>禁止SELECT...FOR UPDATE等显式加锁</t>
+  </si>
+  <si>
+    <t>检查SQL是否包含FOR UPDATE</t>
+  </si>
+  <si>
+    <t>使用显式锁：业务SQL包含SELECT...FOR UPDATE等加锁操作。</t>
+  </si>
+  <si>
+    <t>移除显式锁并按既定并发控制方案重新设计。</t>
+  </si>
+  <si>
+    <t>BUS-012</t>
+  </si>
+  <si>
+    <t>批量INSERT单次VALUES不超过5000个元组</t>
+  </si>
+  <si>
+    <t>检查INSERT的VALUES列表数量</t>
+  </si>
+  <si>
+    <t>批量插入超过上限：单条INSERT的VALUES数量超过5000。</t>
+  </si>
+  <si>
+    <t>拆分批次，确保每条INSERT不超过5000个VALUES元组。</t>
+  </si>
+  <si>
+    <t>BUS-013</t>
+  </si>
+  <si>
+    <t>禁止使用随机排序函数（RAND()/RANDOM()/DBMS_RANDOM.VALUE等）</t>
+  </si>
+  <si>
+    <t>检查ORDER BY是否使用随机排序函数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用随机排序函数：检测到&lt;function&gt;随机查询。</t>
+  </si>
+  <si>
+    <t>移除随机排序函数，改用可控的抽样或随机键方案。</t>
+  </si>
+  <si>
+    <t>应用代码扫描汇总</t>
+  </si>
+  <si>
+    <t>统计项</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>SQL 总数</t>
+  </si>
+  <si>
+    <t>通过数</t>
+  </si>
+  <si>
+    <t>不通过数</t>
+  </si>
+  <si>
+    <t>SQL 数量</t>
+  </si>
+  <si>
+    <t>未识别</t>
+  </si>
+  <si>
+    <t>规则 ID</t>
+  </si>
+  <si>
+    <t>命中次数</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,8 +376,39 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1F2937"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1F2937"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFDC2626"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -125,8 +420,38 @@
         <fgColor rgb="FF44546A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E3A5F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEE2E2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -173,11 +498,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9DEE7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9DEE7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9DEE7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9DEE7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -194,6 +549,48 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -553,4 +950,521 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38B441AD-5812-498D-8B89-2CC3CEF9A76C}">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="20"/>
+    </row>
+    <row r="3" spans="1:2" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="22"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="22"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="22"/>
+    </row>
+    <row r="8" spans="1:2" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="22"/>
+    </row>
+    <row r="12" spans="1:2" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="22"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="22"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="22"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="22"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE2A170C-52B5-454E-95BF-F647A2735DEC}">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="50.1640625" customWidth="1"/>
+    <col min="6" max="6" width="35.9140625" customWidth="1"/>
+    <col min="7" max="7" width="32.08203125" customWidth="1"/>
+    <col min="8" max="8" width="31.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+    </row>
+    <row r="4" spans="1:8" ht="29" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="143" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="117" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="52" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="104" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="104" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="117" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="78" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="91" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="65" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="104" x14ac:dyDescent="0.3">
+      <c r="A14" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="91" x14ac:dyDescent="0.3">
+      <c r="A15" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="78" x14ac:dyDescent="0.3">
+      <c r="A16" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="91" x14ac:dyDescent="0.3">
+      <c r="A17" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/sql-audit/assets/应用代码扫描结果模板.xlsx
+++ b/sql-audit/assets/应用代码扫描结果模板.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
   <si>
     <t>人工复核结果</t>
   </si>
@@ -445,6 +445,21 @@
   </si>
   <si>
     <t>为条件列创建合适的索引，或调整查询条件以利用现有索引；若无法确认索引情况，请补充数据模型后重新审核。</t>
+  </si>
+  <si>
+    <t>业务 SQL 中的 SELECT、DELETE 和 UPDATE 语句必须包含有效的 WHERE 条件，用于限定查询或实际操作的数据范围。仅包含恒真条件（如 WHERE 1=1）且无其他实际过滤条件的，视为无效 WHERE，属于违规。若 WHERE 中包含具体过滤条件（如 id=?、status=?），即使同时存在 1=1，也不视为违规。</t>
+  </si>
+  <si>
+    <t>检查 SELECT、DELETE 和 UPDATE 是否包含 WHERE 及实际过滤条件；仅由恒真条件组成时判定违规；仅检查业务 SQL 本身</t>
+  </si>
+  <si>
+    <t>SELECT、DELETE/UPDATE 缺少有效 WHERE 条件，可能导致全表扫描或对全表执行删除、更新操作。</t>
+  </si>
+  <si>
+    <t>为 SELECT、DELETE/UPDATE 添加具体业务过滤条件（如主键、唯一键或明确的业务状态），确保仅查询或影响目标数据范围。</t>
+  </si>
+  <si>
+    <t>禁止不带条件的查询和数据变更语句</t>
   </si>
 </sst>
 </file>
@@ -1297,7 +1312,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>55</v>
+        <v>125</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>18</v>
@@ -1309,16 +1324,16 @@
         <v>20</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>57</v>
+        <v>122</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>58</v>
+        <v>123</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="69" x14ac:dyDescent="0.3">

--- a/sql-audit/assets/应用代码扫描结果模板.xlsx
+++ b/sql-audit/assets/应用代码扫描结果模板.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\All\xinju\AI-9\sql-audit\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477672DA-F5DD-4DBF-A511-0FCAD9E250B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47BD94E1-E8EB-40F9-840A-7116757B9475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="121">
   <si>
     <t>人工复核结果</t>
   </si>
@@ -48,10 +48,6 @@
   </si>
   <si>
     <t>原SQL</t>
-  </si>
-  <si>
-    <t>xxxx.sql</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>SELECT 1 FROM  &lt;include refid="tableName"/&gt; WHERE alarm_id = #{alarmId} LIMIT 1</t>
@@ -202,24 +198,6 @@
   </si>
   <si>
     <t>去除 DDL 语句，将结构变更操作移交 DBA 或运维通过变更流程执行；如确需清理数据，改用 DELETE 并分批提交。</t>
-  </si>
-  <si>
-    <t>禁止不带条件的DML语句</t>
-  </si>
-  <si>
-    <t>DELETE 和 UPDATE 语句必须包含有效的 WHERE 条件，用于限定实际操作的数据范围。仅包含恒真条件（如 WHERE 1=1）且无其他实际过滤条件的，视为无效 WHERE，属于违规。若 WHERE 中包含具体过滤条件（如 id=?、status=?），即使同时存在 1=1，也不视为违规。</t>
-  </si>
-  <si>
-    <t>1、检查 DELETE/UPDATE 语句是否包含 WHERE 子句。
-2、若包含 WHERE，检查其中是否含有实际过滤条件（非恒真条件，如 1=1、true 等）。
-3、若 WHERE 仅由恒真条件组成且无其他条件，判定违规。
-4、若 WHERE 中包含具体字段条件或参数条件，判定合规。</t>
-  </si>
-  <si>
-    <t>DELETE/UPDATE 缺少有效 WHERE 条件，可能对全表执行删除或更新操作。</t>
-  </si>
-  <si>
-    <t>为 DELETE/UPDATE 添加具体业务过滤条件（如主键、唯一键或明确的业务状态），确保仅影响目标行。</t>
   </si>
   <si>
     <t>建议使用显式字段声明</t>
@@ -460,6 +438,10 @@
   </si>
   <si>
     <t>禁止不带条件的查询和数据变更语句</t>
+  </si>
+  <si>
+    <t>xxxx.sql（第x行）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -731,43 +713,43 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1090,62 +1072,62 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>10</v>
-      </c>
       <c r="F2" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" s="7"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>7</v>
+        <v>120</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>9</v>
-      </c>
       <c r="E3" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>7</v>
+        <v>120</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>9</v>
-      </c>
       <c r="E4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>45</v>
       </c>
       <c r="G4" s="7"/>
     </row>
@@ -1165,54 +1147,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="12"/>
+      <c r="A1" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="23"/>
     </row>
     <row r="3" spans="1:2" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="6"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" s="6"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B6" s="6"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7" s="6"/>
     </row>
     <row r="9" spans="1:2" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>41</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" s="6">
         <v>1</v>
@@ -1220,7 +1202,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" s="6">
         <v>1</v>
@@ -1250,438 +1232,438 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="D1" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="115" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="14" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="115" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="C2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="D2" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="G2" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="126.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="E3" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="H2" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="I2" s="18" t="s">
+      <c r="F3" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="115" x14ac:dyDescent="0.3">
-      <c r="A3" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="C3" s="16" t="s">
+      <c r="C4" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="E4" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="G3" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="H3" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="I3" s="21" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="69" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="16" t="s">
+      <c r="F4" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="92" x14ac:dyDescent="0.3">
+      <c r="A5" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="G5" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="80.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="115" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="92" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="B8" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="I4" s="18" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="92" x14ac:dyDescent="0.3">
-      <c r="A5" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" s="16" t="s">
+      <c r="F8" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="115" x14ac:dyDescent="0.3">
+      <c r="A9" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="E9" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="G5" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="H5" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="I5" s="21" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="80.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="16" t="s">
+      <c r="F9" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="115" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="E10" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="H6" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="I6" s="18" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="115" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
+      <c r="F10" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="115" x14ac:dyDescent="0.3">
+      <c r="A11" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="20" t="s">
+      <c r="D11" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="G7" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="H7" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="I7" s="21" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="92" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" s="16" t="s">
+      <c r="F11" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="80.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="E12" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H8" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="I8" s="18" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="115" x14ac:dyDescent="0.3">
-      <c r="A9" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" s="16" t="s">
+      <c r="F12" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="92" x14ac:dyDescent="0.3">
+      <c r="A13" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="E13" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="G9" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="H9" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="I9" s="21" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="115" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="C10" s="16" t="s">
+      <c r="F13" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="I13" s="19" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="103.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="E14" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="H10" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="I10" s="18" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="115" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="20" t="s">
+      <c r="F14" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="126.5" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="G11" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="H11" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="I11" s="21" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="80.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="H12" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="I12" s="18" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="92" x14ac:dyDescent="0.3">
-      <c r="A13" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="G13" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="H13" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="I13" s="21" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="103.5" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="18" t="s">
+      <c r="F15" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G15" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="H14" s="18" t="s">
+      <c r="H15" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="I14" s="18" t="s">
+      <c r="I15" s="16" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="126.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="H15" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="I15" s="18" t="s">
-        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/sql-audit/assets/应用代码扫描结果模板.xlsx
+++ b/sql-audit/assets/应用代码扫描结果模板.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="133">
   <si>
     <t>人工复核结果</t>
   </si>
@@ -443,12 +443,49 @@
     <t>xxxx.sql（第x行）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>mapper/UserMapper.xml（第42行）</t>
+  </si>
+  <si>
+    <t>Mysql</t>
+  </si>
+  <si>
+    <t>SELECT user_id, user_name FROM users WHERE user_id = #{userId}</t>
+  </si>
+  <si>
+    <t>mapper/UserMapper.xml（第51行）</t>
+  </si>
+  <si>
+    <t>SELECT * FROM users WHERE user_id = #{userId}</t>
+  </si>
+  <si>
+    <t>1. BUS-003【建议】使用 SELECT * 未显式指定查询字段，返回列不明确，可能包含不需要的列。</t>
+  </si>
+  <si>
+    <t>1. 建议将 SELECT * 改为显式列出实际需要的字段名。</t>
+  </si>
+  <si>
+    <t>mapper/UserMapper.xml（第58行）</t>
+  </si>
+  <si>
+    <t>SELECT * FROM users</t>
+  </si>
+  <si>
+    <t>不通过</t>
+  </si>
+  <si>
+    <t>1. BUS-002【硬性】SELECT、DELETE/UPDATE 缺少有效 WHERE 条件，可能导致全表扫描或对全表执行删除、更新操作。；2. BUS-003【建议】使用 SELECT * 未显式指定查询字段，返回列不明确，可能包含不需要的列。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 为 SELECT、DELETE/UPDATE 添加具体业务过滤条件（如主键、唯一键或明确的业务状态），确保仅查询或影响目标数据范围。
+2. 建议将 SELECT * 改为显式列出实际需要的字段名。</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -509,8 +546,62 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F2937"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF991B1B"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF92400E"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF166534"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1F2937"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -519,18 +610,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF44546A"/>
+        <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
+        <fgColor rgb="FF1F4E78"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7F9FC"/>
+        <fgColor rgb="FFF8FAFC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -560,13 +651,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="65"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEE2E2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF4CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -689,7 +798,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -750,6 +859,42 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1038,98 +1183,100 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.5" customWidth="1"/>
-    <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="13.1640625" customWidth="1"/>
-    <col min="4" max="4" width="15.1640625" customWidth="1"/>
-    <col min="5" max="5" width="12.25" customWidth="1"/>
-    <col min="6" max="6" width="13.1640625" customWidth="1"/>
-    <col min="7" max="7" width="17.1640625" customWidth="1"/>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="48" customWidth="1"/>
+    <col min="6" max="6" width="52" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="24" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="8" t="s">
+      <c r="A2" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D2" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="7"/>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>22</v>
-      </c>
+      <c r="A3" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="26"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="7"/>
+      <c r="A4" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="G4" s="26"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1143,52 +1290,53 @@
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:2" ht="28" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="23"/>
+      <c r="B1" s="24"/>
     </row>
     <row r="3" spans="1:2" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="24" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="6"/>
+      <c r="B4" s="26"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="6"/>
+      <c r="B5" s="26"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="6"/>
+      <c r="B6" s="26"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="6"/>
+      <c r="B7" s="26"/>
     </row>
     <row r="9" spans="1:2" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="24" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1222,447 +1370,449 @@
   <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="14.4140625" customWidth="1"/>
-    <col min="6" max="6" width="35.9140625" customWidth="1"/>
-    <col min="7" max="7" width="32.08203125" customWidth="1"/>
-    <col min="8" max="8" width="31.25" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="42" customWidth="1"/>
+    <col min="7" max="7" width="42" customWidth="1"/>
+    <col min="8" max="8" width="38" customWidth="1"/>
+    <col min="9" max="9" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:9" ht="28" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="24" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="115" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="33" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="126.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="I3" s="25" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="69" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="H4" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="33" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="92" x14ac:dyDescent="0.3">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="25" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="80.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="I6" s="16" t="s">
+      <c r="I6" s="33" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="115" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="I7" s="19" t="s">
+      <c r="I7" s="25" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="92" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="H8" s="16" t="s">
+      <c r="H8" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="I8" s="33" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="115" x14ac:dyDescent="0.3">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="H9" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="I9" s="19" t="s">
+      <c r="I9" s="25" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="115" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="H10" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="I10" s="16" t="s">
+      <c r="I10" s="33" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="115" x14ac:dyDescent="0.3">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="H11" s="19" t="s">
+      <c r="H11" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="I11" s="19" t="s">
+      <c r="I11" s="25" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="80.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="H12" s="16" t="s">
+      <c r="H12" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="I12" s="16" t="s">
+      <c r="I12" s="33" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="92" x14ac:dyDescent="0.3">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="H13" s="19" t="s">
+      <c r="H13" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="I13" s="19" t="s">
+      <c r="I13" s="25" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="103.5" x14ac:dyDescent="0.3">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="H14" s="16" t="s">
+      <c r="H14" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="I14" s="16" t="s">
+      <c r="I14" s="33" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="126.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="21" t="s">
+      <c r="F15" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="G15" s="16" t="s">
+      <c r="G15" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="H15" s="16" t="s">
+      <c r="H15" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="I15" s="16" t="s">
+      <c r="I15" s="25" t="s">
         <v>114</v>
       </c>
     </row>

--- a/sql-audit/assets/应用代码扫描结果模板.xlsx
+++ b/sql-audit/assets/应用代码扫描结果模板.xlsx
@@ -188,10 +188,11 @@
     <t>业务 SQL 中禁止包含任何数据定义语言（DDL）操作，包括但不限于 TRUNCATE、CREATE、ALTER、DROP、RENAME、COMMENT、GRANT、REVOKE。也禁止通过动态 SQL 拼接后在业务 SQL 中执行 DDL。适用范围仅限业务 SQL，不包含数据库对象内部定义</t>
   </si>
   <si>
-    <t>1、检查业务 SQL 文本中是否出现 TRUNCATE、CREATE、ALTER、DROP、RENAME 等 DDL 关键字。
+    <t xml:space="preserve">1、检查业务 SQL 文本中是否出现 TRUNCATE、CREATE、ALTER、DROP、RENAME 等 DDL 关键字。
 2、忽略字符串常量、注释中的关键字，避免误报。
 3、检查动态 SQL 拼接内容，若其中包含 DDL 关键字同样判定违规。
-4、仅检查业务 SQL 本身，不检查存储过程、函数等对象内部定义。</t>
+4、CREATE TABLE被允许，应判定为合法。
+5、仅检查业务 SQL 本身，不检查存储过程、函数等对象内部定义。</t>
   </si>
   <si>
     <t>业务 SQL 中直接包含 DDL 语句，属于高危操作，可能引发锁表、数据丢失或意外结构变更。</t>
@@ -260,13 +261,13 @@
     <t>业务 SQL 中建议尽量避免使用 NOT、!=、&lt;&gt;、NOT EXISTS、NOT IN 等负向查询条件，优先考虑使用正向条件或等价改写。适用范围仅限业务 SQL，不包含数据库对象内部定义。</t>
   </si>
   <si>
-    <t>1、检查 SQL 中是否出现 NOT、!=、&lt;&gt;、NOT EXISTS、NOT IN 等负向查询关键字或运算符。
+    <t xml:space="preserve">1、检查 WHERE 子句中是否出现 NOT、!=、&lt;&gt;、NOT EXISTS、NOT IN 等负向查询关键字或运算符。
 2、若出现，则给出优化建议，不判定为违规。
 3、忽略字符串常量、注释中的关键字，避免误报。
 4、仅检查业务 SQL 本身。</t>
   </si>
   <si>
-    <t>使用负向查询可能导致索引失效、全表扫描，影响查询性能。</t>
+    <t>使用负向查询可能导致SQL不走索引、全表扫描，影响查询性能。</t>
   </si>
   <si>
     <t>建议改写为正向条件，如使用 IN 替代 NOT IN（需注意 NULL 值处理），或使用 EXISTS 替代 NOT EXISTS 等。</t>
